--- a/data/gravel/Slug Gasser 2025.xlsx
+++ b/data/gravel/Slug Gasser 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11018"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{63D6A8B1-78A1-CE4C-A94F-323C9EF58017}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3833095-FB47-734B-BB75-2C579657CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="7400" yWindow="2760" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
   <si>
     <t>brand</t>
   </si>
@@ -360,6 +360,24 @@
   </si>
   <si>
     <t>a8:g33</t>
+  </si>
+  <si>
+    <t>head_tube_d</t>
+  </si>
+  <si>
+    <t>headset_upper</t>
+  </si>
+  <si>
+    <t>headset_lower</t>
+  </si>
+  <si>
+    <t>fork_steerer</t>
+  </si>
+  <si>
+    <t>fork_steerer_d</t>
+  </si>
+  <si>
+    <t>fork_material</t>
   </si>
 </sst>
 </file>
@@ -746,7 +764,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O74"/>
+  <dimension ref="A1:O80"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -1439,162 +1457,192 @@
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B50" s="1" t="s">
-        <v>106</v>
+        <v>109</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>43</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>44</v>
+        <v>111</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B53" s="1">
-        <v>31.6</v>
+        <v>112</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B54" s="1">
-        <v>36</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>47</v>
+        <v>114</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>48</v>
+        <v>42</v>
+      </c>
+      <c r="B56" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>49</v>
+        <v>43</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>50</v>
+        <v>44</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B59" s="1" t="s">
-        <v>80</v>
+        <v>45</v>
+      </c>
+      <c r="B59" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B60" s="1" t="s">
-        <v>69</v>
+        <v>46</v>
+      </c>
+      <c r="B60" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>53</v>
+        <v>47</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>54</v>
+        <v>48</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B63" s="1">
-        <v>2</v>
+        <v>49</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B64" s="1">
-        <v>1</v>
+        <v>50</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>57</v>
+        <v>51</v>
+      </c>
+      <c r="B65" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>58</v>
+        <v>52</v>
+      </c>
+      <c r="B66" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>59</v>
+        <v>53</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>60</v>
+        <v>54</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>61</v>
+        <v>55</v>
+      </c>
+      <c r="B69" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B70" s="1">
-        <v>2700</v>
-      </c>
-      <c r="C70" s="1" t="s">
-        <v>104</v>
+        <v>1</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B71" s="1">
-        <v>5900</v>
+        <v>57</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>64</v>
+        <v>58</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B73" s="1" t="s">
-        <v>74</v>
+        <v>59</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="75" spans="1:3">
+      <c r="A75" s="1" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="76" spans="1:3">
+      <c r="A76" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="B76" s="1">
+        <v>2700</v>
+      </c>
+      <c r="C76" s="1" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="77" spans="1:3">
+      <c r="A77" s="1" t="s">
+        <v>63</v>
+      </c>
+      <c r="B77" s="1">
+        <v>5900</v>
+      </c>
+    </row>
+    <row r="78" spans="1:3">
+      <c r="A78" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="79" spans="1:3">
+      <c r="A79" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B79" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="80" spans="1:3">
+      <c r="A80" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B74" s="1" t="s">
+      <c r="B80" s="1" t="s">
         <v>82</v>
       </c>
     </row>

--- a/data/gravel/Slug Gasser 2025.xlsx
+++ b/data/gravel/Slug Gasser 2025.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11122"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/walker/Documents/Github/Bike Geometry Project/data/gravel/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3833095-FB47-734B-BB75-2C579657CB9B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26B373A4-6BA2-4444-9891-E49C0AB657CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="7200" yWindow="500" windowWidth="28800" windowHeight="17500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="116" uniqueCount="115">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="118" uniqueCount="117">
   <si>
     <t>brand</t>
   </si>
@@ -359,9 +359,6 @@
     <t>Geo numbers are shown static, un-sagged</t>
   </si>
   <si>
-    <t>a8:g33</t>
-  </si>
-  <si>
     <t>head_tube_d</t>
   </si>
   <si>
@@ -378,6 +375,15 @@
   </si>
   <si>
     <t>fork_material</t>
+  </si>
+  <si>
+    <t>fork_travel</t>
+  </si>
+  <si>
+    <t>fork_sag</t>
+  </si>
+  <si>
+    <t>a8:g35</t>
   </si>
 </sst>
 </file>
@@ -764,7 +770,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:O80"/>
+  <dimension ref="A1:O82"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
     <col min="1" max="2" width="19.6640625" style="1" customWidth="1"/>
@@ -822,7 +828,7 @@
         <v>5</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>108</v>
+        <v>116</v>
       </c>
     </row>
     <row r="8" spans="1:15">
@@ -1210,439 +1216,481 @@
     </row>
     <row r="23" spans="1:9" ht="21" customHeight="1">
       <c r="A23" s="1" t="s">
+        <v>114</v>
+      </c>
+      <c r="C23" s="7">
+        <v>120</v>
+      </c>
+      <c r="D23" s="7">
+        <v>120</v>
+      </c>
+      <c r="E23" s="7">
+        <v>120</v>
+      </c>
+      <c r="F23" s="7">
+        <v>120</v>
+      </c>
+      <c r="G23" s="7">
+        <v>120</v>
+      </c>
+      <c r="H23" s="7"/>
+    </row>
+    <row r="24" spans="1:9" ht="21" customHeight="1">
+      <c r="A24" s="1" t="s">
+        <v>115</v>
+      </c>
+      <c r="C24" s="7">
+        <v>0</v>
+      </c>
+      <c r="D24" s="7">
+        <v>0</v>
+      </c>
+      <c r="E24" s="7">
+        <v>0</v>
+      </c>
+      <c r="F24" s="7">
+        <v>0</v>
+      </c>
+      <c r="G24" s="7">
+        <v>0</v>
+      </c>
+      <c r="H24" s="7"/>
+    </row>
+    <row r="25" spans="1:9" ht="21" customHeight="1">
+      <c r="A25" s="1" t="s">
         <v>66</v>
       </c>
-      <c r="C23" s="7"/>
-      <c r="D23" s="7"/>
-      <c r="E23" s="7"/>
-      <c r="F23" s="7"/>
-      <c r="G23" s="7"/>
-      <c r="H23" s="7"/>
-    </row>
-    <row r="24" spans="1:9">
-      <c r="A24" s="1" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9">
-      <c r="A25" s="1" t="s">
-        <v>20</v>
-      </c>
+      <c r="C25" s="7"/>
+      <c r="D25" s="7"/>
+      <c r="E25" s="7"/>
+      <c r="F25" s="7"/>
+      <c r="G25" s="7"/>
+      <c r="H25" s="7"/>
     </row>
     <row r="26" spans="1:9">
       <c r="A26" s="1" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="1:9">
       <c r="A27" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="C27" s="4"/>
-      <c r="D27" s="4"/>
-      <c r="E27" s="4"/>
+        <v>20</v>
+      </c>
     </row>
     <row r="28" spans="1:9">
       <c r="A28" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="C28" s="4"/>
-      <c r="D28" s="4"/>
-      <c r="E28" s="4"/>
-      <c r="F28" s="4"/>
+        <v>21</v>
+      </c>
     </row>
     <row r="29" spans="1:9">
       <c r="A29" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="C29" s="8">
-        <v>700</v>
-      </c>
-      <c r="D29" s="8">
-        <v>700</v>
-      </c>
-      <c r="E29" s="8">
-        <v>700</v>
-      </c>
-      <c r="F29" s="8">
-        <v>700</v>
-      </c>
-      <c r="G29" s="8">
-        <v>700</v>
-      </c>
-      <c r="H29" s="8"/>
-      <c r="I29" s="8"/>
+        <v>13</v>
+      </c>
+      <c r="C29" s="4"/>
+      <c r="D29" s="4"/>
+      <c r="E29" s="4"/>
     </row>
     <row r="30" spans="1:9">
       <c r="A30" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="C30" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="D30" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="E30" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="F30" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="G30" s="8">
-        <v>2.4</v>
-      </c>
-      <c r="H30" s="8"/>
-      <c r="I30" s="8"/>
+        <v>68</v>
+      </c>
+      <c r="C30" s="4"/>
+      <c r="D30" s="4"/>
+      <c r="E30" s="4"/>
+      <c r="F30" s="4"/>
     </row>
     <row r="31" spans="1:9">
       <c r="A31" s="1" t="s">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="C31" s="8">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="D31" s="8">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="E31" s="8">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="F31" s="8">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="G31" s="8">
-        <v>2.6</v>
+        <v>700</v>
       </c>
       <c r="H31" s="8"/>
       <c r="I31" s="8"/>
     </row>
     <row r="32" spans="1:9">
       <c r="A32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="D32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="E32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="F32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="G32" s="8">
+        <v>2.4</v>
+      </c>
+      <c r="H32" s="8"/>
+      <c r="I32" s="8"/>
+    </row>
+    <row r="33" spans="1:9">
+      <c r="A33" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C33" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="D33" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="E33" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="F33" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="G33" s="8">
+        <v>2.6</v>
+      </c>
+      <c r="H33" s="8"/>
+      <c r="I33" s="8"/>
+    </row>
+    <row r="34" spans="1:9">
+      <c r="A34" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="C32" s="4"/>
-      <c r="D32" s="4"/>
-      <c r="E32" s="4"/>
-      <c r="F32" s="4"/>
-      <c r="G32" s="4"/>
-    </row>
-    <row r="33" spans="1:7">
-      <c r="A33" s="1" t="s">
+      <c r="C34" s="4"/>
+      <c r="D34" s="4"/>
+      <c r="E34" s="4"/>
+      <c r="F34" s="4"/>
+      <c r="G34" s="4"/>
+    </row>
+    <row r="35" spans="1:9">
+      <c r="A35" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="C33" s="4"/>
-      <c r="D33" s="4"/>
-      <c r="E33" s="4"/>
-      <c r="F33" s="4"/>
-      <c r="G33" s="4"/>
-    </row>
-    <row r="34" spans="1:7">
-      <c r="D34" s="5"/>
-      <c r="E34" s="5"/>
-    </row>
-    <row r="35" spans="1:7">
-      <c r="A35" s="1" t="s">
+      <c r="C35" s="4"/>
+      <c r="D35" s="4"/>
+      <c r="E35" s="4"/>
+      <c r="F35" s="4"/>
+      <c r="G35" s="4"/>
+    </row>
+    <row r="36" spans="1:9">
+      <c r="D36" s="5"/>
+      <c r="E36" s="5"/>
+    </row>
+    <row r="37" spans="1:9">
+      <c r="A37" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B35" s="1" t="s">
+      <c r="B37" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="C35" s="4"/>
-      <c r="D35" s="6"/>
-      <c r="E35" s="6"/>
-      <c r="F35" s="4"/>
-    </row>
-    <row r="36" spans="1:7">
-      <c r="A36" s="1" t="s">
-        <v>70</v>
-      </c>
-      <c r="B36" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="D36" s="6"/>
-      <c r="E36" s="6"/>
-    </row>
-    <row r="37" spans="1:7">
-      <c r="A37" s="1" t="s">
-        <v>71</v>
-      </c>
-      <c r="B37" s="1" t="s">
-        <v>83</v>
-      </c>
+      <c r="C37" s="4"/>
       <c r="D37" s="6"/>
       <c r="E37" s="6"/>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="F37" s="4"/>
+    </row>
+    <row r="38" spans="1:9">
       <c r="A38" s="1" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="B38" s="1" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="D38" s="6"/>
       <c r="E38" s="6"/>
     </row>
-    <row r="39" spans="1:7">
+    <row r="39" spans="1:9">
       <c r="A39" s="1" t="s">
-        <v>31</v>
+        <v>71</v>
       </c>
       <c r="B39" s="1" t="s">
-        <v>79</v>
+        <v>83</v>
       </c>
       <c r="D39" s="6"/>
       <c r="E39" s="6"/>
     </row>
-    <row r="40" spans="1:7">
+    <row r="40" spans="1:9">
       <c r="A40" s="1" t="s">
+        <v>72</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="6"/>
+      <c r="E40" s="6"/>
+    </row>
+    <row r="41" spans="1:9">
+      <c r="A41" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>79</v>
+      </c>
+      <c r="D41" s="6"/>
+      <c r="E41" s="6"/>
+    </row>
+    <row r="42" spans="1:9">
+      <c r="A42" s="1" t="s">
         <v>32</v>
       </c>
-      <c r="B40" s="1" t="s">
+      <c r="B42" s="1" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="41" spans="1:7">
-      <c r="A41" s="1" t="s">
+    <row r="43" spans="1:9">
+      <c r="A43" s="1" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="42" spans="1:7">
-      <c r="A42" s="1" t="s">
+    <row r="44" spans="1:9">
+      <c r="A44" s="1" t="s">
         <v>34</v>
       </c>
-      <c r="B42" s="1">
+      <c r="B44" s="1">
         <v>2.6</v>
       </c>
     </row>
-    <row r="43" spans="1:7">
-      <c r="A43" s="1" t="s">
+    <row r="45" spans="1:9">
+      <c r="A45" s="1" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="44" spans="1:7">
-      <c r="A44" s="1" t="s">
+    <row r="46" spans="1:9">
+      <c r="A46" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="B44" s="1">
+      <c r="B46" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="45" spans="1:7">
-      <c r="A45" s="1" t="s">
+    <row r="47" spans="1:9">
+      <c r="A47" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B45" s="1">
+      <c r="B47" s="1">
         <v>120</v>
       </c>
     </row>
-    <row r="46" spans="1:7">
-      <c r="A46" s="1" t="s">
+    <row r="48" spans="1:9">
+      <c r="A48" s="1" t="s">
         <v>38</v>
-      </c>
-    </row>
-    <row r="47" spans="1:7">
-      <c r="A47" s="1" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="48" spans="1:7">
-      <c r="A48" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="49" spans="1:2">
       <c r="A49" s="1" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="50" spans="1:2">
       <c r="A50" s="1" t="s">
-        <v>109</v>
+        <v>40</v>
       </c>
     </row>
     <row r="51" spans="1:2">
       <c r="A51" s="1" t="s">
-        <v>110</v>
+        <v>41</v>
       </c>
     </row>
     <row r="52" spans="1:2">
       <c r="A52" s="1" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:2">
       <c r="A53" s="1" t="s">
-        <v>112</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" spans="1:2">
       <c r="A54" s="1" t="s">
-        <v>113</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:2">
       <c r="A55" s="1" t="s">
-        <v>114</v>
+        <v>111</v>
       </c>
     </row>
     <row r="56" spans="1:2">
       <c r="A56" s="1" t="s">
-        <v>42</v>
-      </c>
-      <c r="B56" s="1" t="s">
-        <v>106</v>
+        <v>112</v>
       </c>
     </row>
     <row r="57" spans="1:2">
       <c r="A57" s="1" t="s">
-        <v>43</v>
+        <v>113</v>
       </c>
     </row>
     <row r="58" spans="1:2">
       <c r="A58" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
+      </c>
+      <c r="B58" s="1" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="59" spans="1:2">
       <c r="A59" s="1" t="s">
-        <v>45</v>
-      </c>
-      <c r="B59" s="1">
-        <v>31.6</v>
+        <v>43</v>
       </c>
     </row>
     <row r="60" spans="1:2">
       <c r="A60" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="B60" s="1">
-        <v>36</v>
+        <v>44</v>
       </c>
     </row>
     <row r="61" spans="1:2">
       <c r="A61" s="1" t="s">
-        <v>47</v>
+        <v>45</v>
+      </c>
+      <c r="B61" s="1">
+        <v>31.6</v>
       </c>
     </row>
     <row r="62" spans="1:2">
       <c r="A62" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
+      </c>
+      <c r="B62" s="1">
+        <v>36</v>
       </c>
     </row>
     <row r="63" spans="1:2">
       <c r="A63" s="1" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="64" spans="1:2">
       <c r="A64" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
     </row>
     <row r="65" spans="1:3">
       <c r="A65" s="1" t="s">
-        <v>51</v>
-      </c>
-      <c r="B65" s="1" t="s">
-        <v>80</v>
+        <v>49</v>
       </c>
     </row>
     <row r="66" spans="1:3">
       <c r="A66" s="1" t="s">
-        <v>52</v>
-      </c>
-      <c r="B66" s="1" t="s">
-        <v>69</v>
+        <v>50</v>
       </c>
     </row>
     <row r="67" spans="1:3">
       <c r="A67" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
+      </c>
+      <c r="B67" s="1" t="s">
+        <v>80</v>
       </c>
     </row>
     <row r="68" spans="1:3">
       <c r="A68" s="1" t="s">
-        <v>54</v>
+        <v>52</v>
+      </c>
+      <c r="B68" s="1" t="s">
+        <v>69</v>
       </c>
     </row>
     <row r="69" spans="1:3">
       <c r="A69" s="1" t="s">
-        <v>55</v>
-      </c>
-      <c r="B69" s="1">
-        <v>2</v>
+        <v>53</v>
       </c>
     </row>
     <row r="70" spans="1:3">
       <c r="A70" s="1" t="s">
-        <v>56</v>
-      </c>
-      <c r="B70" s="1">
-        <v>1</v>
+        <v>54</v>
       </c>
     </row>
     <row r="71" spans="1:3">
       <c r="A71" s="1" t="s">
-        <v>57</v>
+        <v>55</v>
+      </c>
+      <c r="B71" s="1">
+        <v>2</v>
       </c>
     </row>
     <row r="72" spans="1:3">
       <c r="A72" s="1" t="s">
-        <v>58</v>
+        <v>56</v>
+      </c>
+      <c r="B72" s="1">
+        <v>1</v>
       </c>
     </row>
     <row r="73" spans="1:3">
       <c r="A73" s="1" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
     </row>
     <row r="74" spans="1:3">
       <c r="A74" s="1" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="75" spans="1:3">
       <c r="A75" s="1" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
     </row>
     <row r="76" spans="1:3">
       <c r="A76" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="B76" s="1">
-        <v>2700</v>
-      </c>
-      <c r="C76" s="1" t="s">
-        <v>104</v>
+        <v>60</v>
       </c>
     </row>
     <row r="77" spans="1:3">
       <c r="A77" s="1" t="s">
-        <v>63</v>
-      </c>
-      <c r="B77" s="1">
-        <v>5900</v>
+        <v>61</v>
       </c>
     </row>
     <row r="78" spans="1:3">
       <c r="A78" s="1" t="s">
-        <v>64</v>
+        <v>62</v>
+      </c>
+      <c r="B78" s="1">
+        <v>2700</v>
+      </c>
+      <c r="C78" s="1" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="79" spans="1:3">
       <c r="A79" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="B79" s="1" t="s">
-        <v>74</v>
+        <v>63</v>
+      </c>
+      <c r="B79" s="1">
+        <v>5900</v>
       </c>
     </row>
     <row r="80" spans="1:3">
       <c r="A80" s="1" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="81" spans="1:2">
+      <c r="A81" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="B81" s="1" t="s">
+        <v>74</v>
+      </c>
+    </row>
+    <row r="82" spans="1:2">
+      <c r="A82" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="B80" s="1" t="s">
+      <c r="B82" s="1" t="s">
         <v>82</v>
       </c>
     </row>
